--- a/data/por_departamento/San Miguel/establecimientos_salud.xlsx
+++ b/data/por_departamento/San Miguel/establecimientos_salud.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Establecimientos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA59"/>
+  <dimension ref="A1:AA58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3441,7 +3441,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>geofabrik-way-401307201</t>
+          <t>geofabrik-way-378566160</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3451,32 +3451,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>way/401307201</t>
+          <t>way/378566160</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Hospital San Francisco.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>edificio</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>San Antonio Del Mosco</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3501,17 +3501,17 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>13.83890875</t>
+          <t>13.48429984</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-88.26617586</t>
+          <t>-88.1850995</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3521,24 +3521,24 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.2662939 13.8389388, -88.2662256 13.8389946, -88.266185 13.8389479, -88.2661018 13.8390159, -88.266035 13.8389389, -88.2662217 13.8387862, -88.2662884 13.8388631, -88.2662532 13.8388919, -88.2662939 13.8389388))</t>
+          <t>POLYGON ((-88.1853709 13.4845657, -88.1853416 13.4845662, -88.1849163 13.484591, -88.1849203 13.4843563, -88.1847822 13.4843485, -88.1847942 13.4840498, -88.1853629 13.4840537, -88.1853709 13.4845657))</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/401307201</t>
+          <t>https://www.openstreetmap.org/way/378566160</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.83890875,-88.26617586</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.48429984,-88.1850995</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>geofabrik-way-378566160</t>
+          <t>geofabrik-way-905258276</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>way/378566160</t>
+          <t>way/905258276</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hospital San Francisco.</t>
+          <t>Hospital Josefino Vilaseca</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3598,17 +3598,17 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>13.48429984</t>
+          <t>13.48013924</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-88.1850995</t>
+          <t>-88.22139133</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -3618,59 +3618,59 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.1853709 13.4845657, -88.1853416 13.4845662, -88.1849163 13.484591, -88.1849203 13.4843563, -88.1847822 13.4843485, -88.1847942 13.4840498, -88.1853629 13.4840537, -88.1853709 13.4845657))</t>
+          <t>POLYGON ((-88.2217238 13.4796837, -88.2216192 13.4806134, -88.2210586 13.4805625, -88.221149 13.4797005, -88.2217238 13.4796837))</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/378566160</t>
+          <t>https://www.openstreetmap.org/way/905258276</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.48429984,-88.1850995</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.48013924,-88.22139133</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>geofabrik-way-905258276</t>
+          <t>hot-way-778682715</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>way/905258276</t>
+          <t>way/778682715</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hospital Josefino Vilaseca</t>
+          <t>Region Oriental De Salud</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>edificio</t>
+          <t>poligono</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3695,17 +3695,17 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>13.48013924</t>
+          <t>13.49595615</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-88.22139133</t>
+          <t>-88.20042914</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -3715,24 +3715,24 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.2217238 13.4796837, -88.2216192 13.4806134, -88.2210586 13.4805625, -88.221149 13.4797005, -88.2217238 13.4796837))</t>
+          <t>POLYGON ((-88.2015367 13.4961093, -88.201467 13.4963858, -88.2006248 13.4962345, -88.2002493 13.4963336, -88.1996431 13.4960623, -88.1996753 13.4953425, -88.2015367 13.4961093))</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/905258276</t>
+          <t>https://www.openstreetmap.org/way/778682715</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.48013924,-88.22139133</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.49595615,-88.20042914</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hot-way-778682715</t>
+          <t>hot-node-1974005866</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3742,32 +3742,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>way/778682715</t>
+          <t>node/1974005866</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Region Oriental De Salud</t>
+          <t>Centro Asistencial de Salud</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sesori</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3787,49 +3787,49 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>13.49595615</t>
+          <t>13.7226235</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-88.20042914</t>
+          <t>-88.3623518</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.2015367 13.4961093, -88.201467 13.4963858, -88.2006248 13.4962345, -88.2002493 13.4963336, -88.1996431 13.4960623, -88.1996753 13.4953425, -88.2015367 13.4961093))</t>
+          <t>POINT (-88.3623518 13.7226235)</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/778682715</t>
+          <t>https://www.openstreetmap.org/node/1974005866</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.49595615,-88.20042914</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7226235,-88.3623518</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hot-node-1974005866</t>
+          <t>hot-node-3987124142</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3839,22 +3839,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>node/1974005866</t>
+          <t>node/3987124142</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Centro Asistencial de Salud</t>
+          <t>Cruz Roja</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sesori</t>
+          <t>Ciudad Barrios</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>13.7226235</t>
+          <t>13.7642841</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>-88.3623518</t>
+          <t>-88.2717482</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -3909,24 +3909,24 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>POINT (-88.3623518 13.7226235)</t>
+          <t>POINT (-88.2717482 13.7642841)</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1974005866</t>
+          <t>https://www.openstreetmap.org/node/3987124142</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7226235,-88.3623518</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7642841,-88.2717482</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hot-node-3987124142</t>
+          <t>hot-node-3971622791</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>node/3987124142</t>
+          <t>node/3971622791</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cruz Roja</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Ciudad Barrios</t>
+          <t>Nuevo Edén de San Juan</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>13.7642841</t>
+          <t>13.825499</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>-88.2717482</t>
+          <t>-88.4877406</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4006,24 +4006,24 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>POINT (-88.2717482 13.7642841)</t>
+          <t>POINT (-88.4877406 13.825499)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3987124142</t>
+          <t>https://www.openstreetmap.org/node/3971622791</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7642841,-88.2717482</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.825499,-88.4877406</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hot-node-3971622791</t>
+          <t>hot-node-3969370292</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>node/3971622791</t>
+          <t>node/3969370292</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nuevo Edén de San Juan</t>
+          <t>San Gerardo</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4076,6 +4076,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>San Gerardo</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4088,12 +4093,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>13.825499</t>
+          <t>13.8102873</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>-88.4877406</t>
+          <t>-88.4048352</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4103,24 +4108,24 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>POINT (-88.4877406 13.825499)</t>
+          <t>POINT (-88.4048352 13.8102873)</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971622791</t>
+          <t>https://www.openstreetmap.org/node/3969370292</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.825499,-88.4877406</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8102873,-88.4048352</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hot-node-3969370292</t>
+          <t>hot-node-12081857874</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4130,12 +4135,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>node/3969370292</t>
+          <t>node/12081857874</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Centro Medico Hemodialisis</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4165,7 +4170,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>San Gerardo</t>
+          <t>El Tránsito</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4173,9 +4178,9 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>San Gerardo</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Privado</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -4190,12 +4195,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>13.8102873</t>
+          <t>13.3530367</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>-88.4048352</t>
+          <t>-88.3479734</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4205,24 +4210,24 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>POINT (-88.4048352 13.8102873)</t>
+          <t>POINT (-88.3479734 13.3530367)</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969370292</t>
+          <t>https://www.openstreetmap.org/node/12081857874</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8102873,-88.4048352</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3530367,-88.3479734</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hot-node-12081857874</t>
+          <t>hot-node-12081857873</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4232,12 +4237,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>node/12081857874</t>
+          <t>node/12081857873</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Centro Medico Hemodialisis</t>
+          <t>Centro Medico El Transito</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4275,11 +4280,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
       <c r="T39" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>13.3530367</t>
+          <t>13.3538052</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>-88.3479734</t>
+          <t>-88.3478837</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4307,24 +4307,24 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>POINT (-88.3479734 13.3530367)</t>
+          <t>POINT (-88.3478837 13.3538052)</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/12081857874</t>
+          <t>https://www.openstreetmap.org/node/12081857873</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3530367,-88.3479734</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3538052,-88.3478837</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hot-node-12081857873</t>
+          <t>hot-node-3982897919</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>node/12081857873</t>
+          <t>node/3982897919</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Centro Medico El Transito</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>13.3538052</t>
+          <t>13.3577238</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>-88.3478837</t>
+          <t>-88.3451317</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4404,24 +4404,24 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>POINT (-88.3478837 13.3538052)</t>
+          <t>POINT (-88.3451317 13.3577238)</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/12081857873</t>
+          <t>https://www.openstreetmap.org/node/3982897919</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3538052,-88.3478837</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3577238,-88.3451317</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hot-node-3982897919</t>
+          <t>hot-node-3976979874</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>node/3982897919</t>
+          <t>node/3976979874</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>El Tránsito</t>
+          <t>San Jorge</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>13.3577238</t>
+          <t>13.4161801</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>-88.3451317</t>
+          <t>-88.3441312</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -4501,24 +4501,24 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>POINT (-88.3451317 13.3577238)</t>
+          <t>POINT (-88.3441312 13.4161801)</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3982897919</t>
+          <t>https://www.openstreetmap.org/node/3976979874</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3577238,-88.3451317</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4161801,-88.3441312</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hot-node-3976979874</t>
+          <t>hot-node-4033946230</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>node/3976979874</t>
+          <t>node/4033946230</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Unidad de Salud La Presita</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>San Jorge</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>13.4161801</t>
+          <t>13.467629</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>-88.3441312</t>
+          <t>-88.1637757</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -4598,24 +4598,24 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>POINT (-88.3441312 13.4161801)</t>
+          <t>POINT (-88.1637757 13.467629)</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3976979874</t>
+          <t>https://www.openstreetmap.org/node/4033946230</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4161801,-88.3441312</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.467629,-88.1637757</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hot-node-4033946230</t>
+          <t>hot-node-4033951128</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4625,22 +4625,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>node/4033946230</t>
+          <t>node/4033951128</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Unidad de Salud La Presita</t>
+          <t>Unidad Médica ISSS</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>13.467629</t>
+          <t>13.4718644</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>-88.1637757</t>
+          <t>-88.1828448</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -4695,24 +4695,24 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>POINT (-88.1637757 13.467629)</t>
+          <t>POINT (-88.1828448 13.4718644)</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4033946230</t>
+          <t>https://www.openstreetmap.org/node/4033951128</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.467629,-88.1637757</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4718644,-88.1828448</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hot-node-4033951128</t>
+          <t>hot-node-3817994597</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>node/4033951128</t>
+          <t>node/3817994597</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Unidad Médica ISSS</t>
+          <t>Electrolab Medic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4765,6 +4765,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4777,12 +4782,12 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>13.4718644</t>
+          <t>13.4737778</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>-88.1828448</t>
+          <t>-88.1842902</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -4792,24 +4797,24 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>POINT (-88.1828448 13.4718644)</t>
+          <t>POINT (-88.1842902 13.4737778)</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4033951128</t>
+          <t>https://www.openstreetmap.org/node/3817994597</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4718644,-88.1828448</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4737778,-88.1842902</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hot-node-3817994597</t>
+          <t>hot-node-2601969391</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4819,22 +4824,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>node/3817994597</t>
+          <t>node/2601969391</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Electrolab Medic</t>
+          <t>Hospital de Especialidades</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4862,11 +4867,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
       <c r="T45" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>13.4737778</t>
+          <t>13.4771514</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>-88.1842902</t>
+          <t>-88.1829557</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -4894,24 +4894,24 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>POINT (-88.1842902 13.4737778)</t>
+          <t>POINT (-88.1829557 13.4771514)</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3817994597</t>
+          <t>https://www.openstreetmap.org/node/2601969391</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4737778,-88.1842902</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4771514,-88.1829557</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hot-node-2601969391</t>
+          <t>hot-node-14132258739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4921,22 +4921,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>node/2601969391</t>
+          <t>node/14132258739</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Hospital de Especialidades</t>
+          <t>clinica hemodialisis + vida</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4964,6 +4964,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nefrología</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>Point</t>
@@ -4976,12 +4981,12 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>13.4771514</t>
+          <t>13.4805516</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>-88.1829557</t>
+          <t>-88.1843417</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -4991,24 +4996,24 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>POINT (-88.1829557 13.4771514)</t>
+          <t>POINT (-88.1843417 13.4805516)</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2601969391</t>
+          <t>https://www.openstreetmap.org/node/14132258739</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4771514,-88.1829557</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4805516,-88.1843417</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hot-node-14132258739</t>
+          <t>hot-node-9394996317</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5018,12 +5023,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>node/14132258739</t>
+          <t>node/9394996317</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>clinica hemodialisis + vida</t>
+          <t>Centro de Salud Familiar</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5061,11 +5066,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Nefrología</t>
-        </is>
-      </c>
       <c r="T47" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5078,12 +5078,12 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>13.4805516</t>
+          <t>13.4819238</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>-88.1843417</t>
+          <t>-88.1795729</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5093,24 +5093,24 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>POINT (-88.1843417 13.4805516)</t>
+          <t>POINT (-88.1795729 13.4819238)</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/14132258739</t>
+          <t>https://www.openstreetmap.org/node/9394996317</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4805516,-88.1843417</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4819238,-88.1795729</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hot-node-9394996317</t>
+          <t>hot-node-13520794420</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5120,22 +5120,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>node/9394996317</t>
+          <t>node/13520794420</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Centro de Salud Familiar</t>
+          <t>Dr. Cristian Flores</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5163,6 +5163,16 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Dermatología</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5175,12 +5185,12 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>13.4819238</t>
+          <t>13.4827509</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>-88.1795729</t>
+          <t>-88.1842793</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5190,24 +5200,24 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>POINT (-88.1795729 13.4819238)</t>
+          <t>POINT (-88.1842793 13.4827509)</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9394996317</t>
+          <t>https://www.openstreetmap.org/node/13520794420</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4819238,-88.1795729</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4827509,-88.1842793</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hot-node-13520794420</t>
+          <t>hot-node-3971572722</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5217,22 +5227,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>node/13520794420</t>
+          <t>node/3971572722</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Dr. Cristian Flores</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Consultorio</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>consultorio</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5252,7 +5262,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Uluazapa</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5260,16 +5270,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Dermatología</t>
-        </is>
-      </c>
       <c r="T49" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>13.4827509</t>
+          <t>13.5041814</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>-88.1842793</t>
+          <t>-88.0716186</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5297,24 +5297,24 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>POINT (-88.1842793 13.4827509)</t>
+          <t>POINT (-88.0716186 13.5041814)</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13520794420</t>
+          <t>https://www.openstreetmap.org/node/3971572722</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.4827509,-88.1842793</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5041814,-88.0716186</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hot-node-3971572722</t>
+          <t>hot-node-3972809696</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5324,22 +5324,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>node/3971572722</t>
+          <t>node/3972809696</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Cruz Roja</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Uluazapa</t>
+          <t>Nueva Guadalupe</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5367,6 +5367,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Chinameca</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5379,12 +5384,12 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>13.5041814</t>
+          <t>13.5113885</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>-88.0716186</t>
+          <t>-88.3478544</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -5394,24 +5399,24 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>POINT (-88.0716186 13.5041814)</t>
+          <t>POINT (-88.3478544 13.5113885)</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971572722</t>
+          <t>https://www.openstreetmap.org/node/3972809696</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5041814,-88.0716186</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5113885,-88.3478544</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>hot-node-3972809696</t>
+          <t>hot-node-3972809679</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5421,12 +5426,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>node/3972809696</t>
+          <t>node/3972809679</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cruz Roja</t>
+          <t>ISSS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5481,12 +5486,12 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>13.5113885</t>
+          <t>13.5121895</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>-88.3478544</t>
+          <t>-88.3469412</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -5496,24 +5501,24 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>POINT (-88.3478544 13.5113885)</t>
+          <t>POINT (-88.3469412 13.5121895)</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3972809696</t>
+          <t>https://www.openstreetmap.org/node/3972809679</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5113885,-88.3478544</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5121895,-88.3469412</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hot-node-3972809679</t>
+          <t>hot-node-3977001154</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5523,22 +5528,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>node/3972809679</t>
+          <t>node/3977001154</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ISSS</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5558,7 +5563,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nueva Guadalupe</t>
+          <t>Quelepa</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5566,11 +5571,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Chinameca</t>
-        </is>
-      </c>
       <c r="T52" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5583,12 +5583,12 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>13.5121895</t>
+          <t>13.5193522</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>-88.3469412</t>
+          <t>-88.2345282</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -5598,24 +5598,24 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>POINT (-88.3469412 13.5121895)</t>
+          <t>POINT (-88.2345282 13.5193522)</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3972809679</t>
+          <t>https://www.openstreetmap.org/node/3977001154</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5121895,-88.3469412</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5193522,-88.2345282</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hot-node-3977001154</t>
+          <t>hot-node-4035752443</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>node/3977001154</t>
+          <t>node/4035752443</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Quelepa</t>
+          <t>Comacarán</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>13.5193522</t>
+          <t>13.5289987</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>-88.2345282</t>
+          <t>-88.067924</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -5695,24 +5695,24 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>POINT (-88.2345282 13.5193522)</t>
+          <t>POINT (-88.067924 13.5289987)</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3977001154</t>
+          <t>https://www.openstreetmap.org/node/4035752443</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5193522,-88.2345282</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5289987,-88.067924</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>hot-node-4035752443</t>
+          <t>hot-node-3977032594</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>node/4035752443</t>
+          <t>node/3977032594</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Comacarán</t>
+          <t>Moncagua</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>13.5289987</t>
+          <t>13.5310736</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>-88.067924</t>
+          <t>-88.2592799</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -5792,24 +5792,24 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>POINT (-88.067924 13.5289987)</t>
+          <t>POINT (-88.2592799 13.5310736)</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4035752443</t>
+          <t>https://www.openstreetmap.org/node/3977032594</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5289987,-88.067924</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5310736,-88.2592799</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hot-node-3977032594</t>
+          <t>hot-node-3972932191</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5819,22 +5819,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>node/3977032594</t>
+          <t>node/3972932191</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Hospital Nacional</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Moncagua</t>
+          <t>Lolotique</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>13.5310736</t>
+          <t>13.5377068</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>-88.2592799</t>
+          <t>-88.3491298</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -5889,24 +5889,24 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>POINT (-88.2592799 13.5310736)</t>
+          <t>POINT (-88.3491298 13.5377068)</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3977032594</t>
+          <t>https://www.openstreetmap.org/node/3972932191</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5310736,-88.2592799</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5377068,-88.3491298</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hot-node-3972932191</t>
+          <t>hot-node-3971511082</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5916,22 +5916,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>node/3972932191</t>
+          <t>node/3971511082</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Hospital Nacional</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>13.5377068</t>
+          <t>13.5540305</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>-88.3491298</t>
+          <t>-88.3509677</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -5986,24 +5986,24 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>POINT (-88.3491298 13.5377068)</t>
+          <t>POINT (-88.3509677 13.5540305)</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3972932191</t>
+          <t>https://www.openstreetmap.org/node/3971511082</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5377068,-88.3491298</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5540305,-88.3509677</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hot-node-3971511082</t>
+          <t>hot-node-8038414002</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6013,22 +6013,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>node/3971511082</t>
+          <t>node/8038414002</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Lolotique</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>13.5540305</t>
+          <t>13.5769823</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>-88.3509677</t>
+          <t>-88.1278297</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6083,24 +6083,24 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>POINT (-88.3509677 13.5540305)</t>
+          <t>POINT (-88.1278297 13.5769823)</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971511082</t>
+          <t>https://www.openstreetmap.org/node/8038414002</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5540305,-88.3509677</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5769823,-88.1278297</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hot-node-8038414002</t>
+          <t>hot-node-3982947146</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6110,22 +6110,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>node/8038414002</t>
+          <t>node/3982947146</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Consultorio</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>consultorio</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chapeltique</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6153,6 +6153,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Chapeltique</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6165,12 +6170,12 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>13.5769823</t>
+          <t>13.6351768</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>-88.1278297</t>
+          <t>-88.2635032</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6180,124 +6185,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>POINT (-88.1278297 13.5769823)</t>
+          <t>POINT (-88.2635032 13.6351768)</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8038414002</t>
+          <t>https://www.openstreetmap.org/node/3982947146</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5769823,-88.1278297</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>hot-node-3982947146</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>node/3982947146</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Unidad de Salud</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Chapeltique</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Oriental</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Chapeltique</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>13.6351768</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>-88.2635032</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>POINT (-88.2635032 13.6351768)</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/3982947146</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=13.6351768,-88.2635032</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA59"/>
+  <autoFilter ref="A1:AA58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>